--- a/prueba ingreso.xlsx
+++ b/prueba ingreso.xlsx
@@ -5,27 +5,38 @@
   <workbookPr/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
-      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="D:\llama\Escritorio\clasificador\"/>
+      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="https://mimposervicios-my.sharepoint.com/personal/practicante2_sistemas_mimpo_com/Documents/Escritorio/clasif/clasificacion/"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{1144DE5A-1BB7-4EA5-A5D9-8B8C635C1535}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="8" documentId="13_ncr:1_{1144DE5A-1BB7-4EA5-A5D9-8B8C635C1535}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{6DAC26EA-98F9-45B3-B996-E660A5B0571F}"/>
   <bookViews>
-    <workbookView xWindow="5760" yWindow="3360" windowWidth="17280" windowHeight="8880" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
+    <workbookView xWindow="28680" yWindow="-90" windowWidth="29040" windowHeight="15720" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
     <sheet name="Sheet1" sheetId="1" r:id="rId1"/>
   </sheets>
-  <calcPr calcId="152511"/>
+  <calcPr calcId="191029"/>
   <extLst>
     <ext xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" uri="{140A7094-0E35-4892-8432-C4D2E57EDEB5}">
       <x15:workbookPr chartTrackingRefBase="1"/>
+    </ext>
+    <ext xmlns:xcalcf="http://schemas.microsoft.com/office/spreadsheetml/2018/calcfeatures" uri="{B58B0392-4F1F-4190-BB64-5DF3571DCE5F}">
+      <xcalcf:calcFeatures>
+        <xcalcf:feature name="microsoft.com:RD"/>
+        <xcalcf:feature name="microsoft.com:Single"/>
+        <xcalcf:feature name="microsoft.com:FV"/>
+        <xcalcf:feature name="microsoft.com:CNMTM"/>
+        <xcalcf:feature name="microsoft.com:LET_WF"/>
+        <xcalcf:feature name="microsoft.com:LAMBDA_WF"/>
+        <xcalcf:feature name="microsoft.com:ARRAYTEXT_WF"/>
+      </xcalcf:calcFeatures>
     </ext>
   </extLst>
 </workbook>
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="14" uniqueCount="6">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="15" uniqueCount="7">
   <si>
     <t>codigo</t>
   </si>
@@ -43,6 +54,9 @@
   </si>
   <si>
     <t>hp</t>
+  </si>
+  <si>
+    <t>clave</t>
   </si>
 </sst>
 </file>
@@ -86,9 +100,10 @@
   <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="2">
+  <cellXfs count="3">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
     <xf numFmtId="0" fontId="1" fillId="0" borderId="0" xfId="0" applyFont="1"/>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyFont="1"/>
   </cellXfs>
   <cellStyles count="1">
     <cellStyle name="Normal" xfId="0" builtinId="0"/>
@@ -369,10 +384,10 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0000-000000000000}">
-  <dimension ref="A2:F12"/>
-  <sheetFormatPr baseColWidth="10" defaultColWidth="8.88671875" defaultRowHeight="14.4" x14ac:dyDescent="0.3"/>
+  <dimension ref="A2:J12"/>
+  <sheetFormatPr baseColWidth="10" defaultColWidth="8.85546875" defaultRowHeight="15" x14ac:dyDescent="0.25"/>
   <sheetData>
-    <row r="2" spans="1:6" x14ac:dyDescent="0.3">
+    <row r="2" spans="1:10" x14ac:dyDescent="0.25">
       <c r="A2" t="s">
         <v>0</v>
       </c>
@@ -380,16 +395,19 @@
         <v>1</v>
       </c>
       <c r="C2" t="s">
+        <v>6</v>
+      </c>
+      <c r="D2" t="s">
         <v>2</v>
       </c>
-      <c r="D2" t="s">
+      <c r="E2" t="s">
         <v>3</v>
       </c>
-      <c r="E2" t="s">
+      <c r="F2" t="s">
         <v>4</v>
       </c>
     </row>
-    <row r="3" spans="1:6" x14ac:dyDescent="0.3">
+    <row r="3" spans="1:10" x14ac:dyDescent="0.25">
       <c r="A3">
         <v>12321</v>
       </c>
@@ -397,16 +415,19 @@
         <v>5</v>
       </c>
       <c r="C3">
+        <v>250</v>
+      </c>
+      <c r="D3">
         <v>11</v>
       </c>
-      <c r="D3">
-        <v>20</v>
-      </c>
       <c r="E3">
         <v>20</v>
       </c>
-    </row>
-    <row r="4" spans="1:6" x14ac:dyDescent="0.3">
+      <c r="F3">
+        <v>20</v>
+      </c>
+    </row>
+    <row r="4" spans="1:10" x14ac:dyDescent="0.25">
       <c r="A4">
         <v>123123</v>
       </c>
@@ -414,17 +435,20 @@
         <v>5</v>
       </c>
       <c r="C4">
+        <v>250</v>
+      </c>
+      <c r="D4">
         <v>11</v>
       </c>
-      <c r="D4">
-        <v>20</v>
-      </c>
       <c r="E4">
         <v>20</v>
       </c>
-      <c r="F4" s="1"/>
-    </row>
-    <row r="5" spans="1:6" x14ac:dyDescent="0.3">
+      <c r="F4">
+        <v>20</v>
+      </c>
+      <c r="G4" s="1"/>
+    </row>
+    <row r="5" spans="1:10" x14ac:dyDescent="0.25">
       <c r="A5">
         <v>1231212</v>
       </c>
@@ -432,16 +456,19 @@
         <v>5</v>
       </c>
       <c r="C5">
+        <v>250</v>
+      </c>
+      <c r="D5">
         <v>22</v>
       </c>
-      <c r="D5">
-        <v>20</v>
-      </c>
       <c r="E5">
         <v>20</v>
       </c>
-    </row>
-    <row r="6" spans="1:6" x14ac:dyDescent="0.3">
+      <c r="F5">
+        <v>20</v>
+      </c>
+    </row>
+    <row r="6" spans="1:10" x14ac:dyDescent="0.25">
       <c r="A6">
         <v>3123124</v>
       </c>
@@ -449,16 +476,19 @@
         <v>5</v>
       </c>
       <c r="C6">
+        <v>250</v>
+      </c>
+      <c r="D6">
         <v>22</v>
       </c>
-      <c r="D6">
-        <v>20</v>
-      </c>
       <c r="E6">
         <v>20</v>
       </c>
-    </row>
-    <row r="7" spans="1:6" x14ac:dyDescent="0.3">
+      <c r="F6">
+        <v>20</v>
+      </c>
+    </row>
+    <row r="7" spans="1:10" x14ac:dyDescent="0.25">
       <c r="A7">
         <v>12313</v>
       </c>
@@ -466,16 +496,20 @@
         <v>5</v>
       </c>
       <c r="C7">
+        <v>250</v>
+      </c>
+      <c r="D7">
         <v>22</v>
       </c>
-      <c r="D7">
-        <v>20</v>
-      </c>
       <c r="E7">
         <v>20</v>
       </c>
-    </row>
-    <row r="8" spans="1:6" x14ac:dyDescent="0.3">
+      <c r="F7">
+        <v>20</v>
+      </c>
+      <c r="J7" s="2"/>
+    </row>
+    <row r="8" spans="1:10" x14ac:dyDescent="0.25">
       <c r="A8">
         <v>123123</v>
       </c>
@@ -483,16 +517,19 @@
         <v>5</v>
       </c>
       <c r="C8">
+        <v>250</v>
+      </c>
+      <c r="D8">
         <v>33</v>
       </c>
-      <c r="D8">
-        <v>20</v>
-      </c>
       <c r="E8">
         <v>20</v>
       </c>
-    </row>
-    <row r="9" spans="1:6" x14ac:dyDescent="0.3">
+      <c r="F8">
+        <v>20</v>
+      </c>
+    </row>
+    <row r="9" spans="1:10" x14ac:dyDescent="0.25">
       <c r="A9">
         <v>12124</v>
       </c>
@@ -500,16 +537,19 @@
         <v>5</v>
       </c>
       <c r="C9">
+        <v>250</v>
+      </c>
+      <c r="D9">
         <v>22</v>
       </c>
-      <c r="D9">
-        <v>20</v>
-      </c>
       <c r="E9">
         <v>20</v>
       </c>
-    </row>
-    <row r="10" spans="1:6" x14ac:dyDescent="0.3">
+      <c r="F9">
+        <v>20</v>
+      </c>
+    </row>
+    <row r="10" spans="1:10" x14ac:dyDescent="0.25">
       <c r="A10">
         <v>123124</v>
       </c>
@@ -517,16 +557,19 @@
         <v>5</v>
       </c>
       <c r="C10">
+        <v>250</v>
+      </c>
+      <c r="D10">
         <v>3</v>
       </c>
-      <c r="D10">
-        <v>20</v>
-      </c>
       <c r="E10">
         <v>20</v>
       </c>
-    </row>
-    <row r="11" spans="1:6" x14ac:dyDescent="0.3">
+      <c r="F10">
+        <v>20</v>
+      </c>
+    </row>
+    <row r="11" spans="1:10" x14ac:dyDescent="0.25">
       <c r="A11">
         <v>124124</v>
       </c>
@@ -534,17 +577,20 @@
         <v>5</v>
       </c>
       <c r="C11">
+        <v>250</v>
+      </c>
+      <c r="D11">
         <v>11</v>
       </c>
-      <c r="D11">
-        <v>20</v>
-      </c>
       <c r="E11">
         <v>20</v>
       </c>
-    </row>
-    <row r="12" spans="1:6" x14ac:dyDescent="0.3">
-      <c r="C12" s="1"/>
+      <c r="F11">
+        <v>20</v>
+      </c>
+    </row>
+    <row r="12" spans="1:10" x14ac:dyDescent="0.25">
+      <c r="D12" s="1"/>
     </row>
   </sheetData>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>

--- a/prueba ingreso.xlsx
+++ b/prueba ingreso.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="https://mimposervicios-my.sharepoint.com/personal/practicante2_sistemas_mimpo_com/Documents/Escritorio/clasif/clasificacion/"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="8" documentId="13_ncr:1_{1144DE5A-1BB7-4EA5-A5D9-8B8C635C1535}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{6DAC26EA-98F9-45B3-B996-E660A5B0571F}"/>
+  <xr:revisionPtr revIDLastSave="12" documentId="13_ncr:1_{1144DE5A-1BB7-4EA5-A5D9-8B8C635C1535}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{DC85C4CC-3332-4D36-9B34-D2285F41F27E}"/>
   <bookViews>
     <workbookView xWindow="28680" yWindow="-90" windowWidth="29040" windowHeight="15720" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
@@ -100,10 +100,9 @@
   <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="3">
+  <cellXfs count="2">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
     <xf numFmtId="0" fontId="1" fillId="0" borderId="0" xfId="0" applyFont="1"/>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyFont="1"/>
   </cellXfs>
   <cellStyles count="1">
     <cellStyle name="Normal" xfId="0" builtinId="0"/>
@@ -384,10 +383,10 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0000-000000000000}">
-  <dimension ref="A2:J12"/>
+  <dimension ref="A2:G12"/>
   <sheetFormatPr baseColWidth="10" defaultColWidth="8.85546875" defaultRowHeight="15" x14ac:dyDescent="0.25"/>
   <sheetData>
-    <row r="2" spans="1:10" x14ac:dyDescent="0.25">
+    <row r="2" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A2" t="s">
         <v>0</v>
       </c>
@@ -407,9 +406,9 @@
         <v>4</v>
       </c>
     </row>
-    <row r="3" spans="1:10" x14ac:dyDescent="0.25">
+    <row r="3" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A3">
-        <v>12321</v>
+        <v>5</v>
       </c>
       <c r="B3" t="s">
         <v>5</v>
@@ -427,9 +426,9 @@
         <v>20</v>
       </c>
     </row>
-    <row r="4" spans="1:10" x14ac:dyDescent="0.25">
+    <row r="4" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A4">
-        <v>123123</v>
+        <v>6</v>
       </c>
       <c r="B4" t="s">
         <v>5</v>
@@ -448,9 +447,9 @@
       </c>
       <c r="G4" s="1"/>
     </row>
-    <row r="5" spans="1:10" x14ac:dyDescent="0.25">
+    <row r="5" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A5">
-        <v>1231212</v>
+        <v>7</v>
       </c>
       <c r="B5" t="s">
         <v>5</v>
@@ -468,9 +467,9 @@
         <v>20</v>
       </c>
     </row>
-    <row r="6" spans="1:10" x14ac:dyDescent="0.25">
+    <row r="6" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A6">
-        <v>3123124</v>
+        <v>8</v>
       </c>
       <c r="B6" t="s">
         <v>5</v>
@@ -488,7 +487,7 @@
         <v>20</v>
       </c>
     </row>
-    <row r="7" spans="1:10" x14ac:dyDescent="0.25">
+    <row r="7" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A7">
         <v>12313</v>
       </c>
@@ -507,9 +506,8 @@
       <c r="F7">
         <v>20</v>
       </c>
-      <c r="J7" s="2"/>
-    </row>
-    <row r="8" spans="1:10" x14ac:dyDescent="0.25">
+    </row>
+    <row r="8" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A8">
         <v>123123</v>
       </c>
@@ -529,7 +527,7 @@
         <v>20</v>
       </c>
     </row>
-    <row r="9" spans="1:10" x14ac:dyDescent="0.25">
+    <row r="9" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A9">
         <v>12124</v>
       </c>
@@ -549,7 +547,7 @@
         <v>20</v>
       </c>
     </row>
-    <row r="10" spans="1:10" x14ac:dyDescent="0.25">
+    <row r="10" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A10">
         <v>123124</v>
       </c>
@@ -569,7 +567,7 @@
         <v>20</v>
       </c>
     </row>
-    <row r="11" spans="1:10" x14ac:dyDescent="0.25">
+    <row r="11" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A11">
         <v>124124</v>
       </c>
@@ -589,7 +587,7 @@
         <v>20</v>
       </c>
     </row>
-    <row r="12" spans="1:10" x14ac:dyDescent="0.25">
+    <row r="12" spans="1:7" x14ac:dyDescent="0.25">
       <c r="D12" s="1"/>
     </row>
   </sheetData>
